--- a/GATEWAY/A1#111#TS23XX/TS23/TServe/V.1.4.46.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#TS23XX/TS23/TServe/V.1.4.46.0/accreditamento-checklist_V8.2.7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\Desktop\TServe\Accreditamento bis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C544895B-2613-470F-9C86-4C5CCE8E4F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC10FFEE-4F1B-4D5C-9BF1-3C43D83DE98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="1785" windowWidth="30675" windowHeight="11910" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6450" yWindow="8250" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -1783,31 +1783,31 @@
     <t>subject_application_id: TServe</t>
   </si>
   <si>
-    <t>2026-02-24T13:22:30Z</t>
-  </si>
-  <si>
-    <t>60a6805e53f67ef025c6321d6ce0920a</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.daaedcaa16^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-02-24T13:32:44Z</t>
-  </si>
-  <si>
-    <t>30170b69925df940038d0f6fa27dcb0f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.ebca2885b3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-02-24T13:37:03Z</t>
-  </si>
-  <si>
-    <t>86359d40e999ad63196eb34cfc095623</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.acfd593793^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-05T10:52:04Z</t>
+  </si>
+  <si>
+    <t>5e8b23030710aee98f38ec230b62d5b4</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.fa57fd07bd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-05T11:01:03Z</t>
+  </si>
+  <si>
+    <t>ae1827f51a8ec3373f0efd8320c0db4d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.7fb50e92af^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-05T11:05:33Z</t>
+  </si>
+  <si>
+    <t>162e5f0ff40a0864717ab5a919508297</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.e86bec11f0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -11151,7 +11151,7 @@
         <v>433</v>
       </c>
       <c r="F191" s="51">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="G191" s="52" t="s">
         <v>464</v>
@@ -11198,7 +11198,7 @@
         <v>434</v>
       </c>
       <c r="F192" s="53">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="G192" s="52" t="s">
         <v>467</v>
@@ -11245,7 +11245,7 @@
         <v>437</v>
       </c>
       <c r="F193" s="37">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="G193" s="37" t="s">
         <v>470</v>
@@ -17508,21 +17508,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17666,32 +17651,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17709,6 +17684,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/A1#111#TS23XX/TS23/TServe/V.1.4.46.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#TS23XX/TS23/TServe/V.1.4.46.0/accreditamento-checklist_V8.2.7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\Desktop\TServe\Accreditamento bis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC10FFEE-4F1B-4D5C-9BF1-3C43D83DE98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B393B7-DE76-4C50-BD07-1AF360E44321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6450" yWindow="8250" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4515" yWindow="2625" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -1783,31 +1783,31 @@
     <t>subject_application_id: TServe</t>
   </si>
   <si>
-    <t>2026-03-05T10:52:04Z</t>
-  </si>
-  <si>
-    <t>5e8b23030710aee98f38ec230b62d5b4</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.fa57fd07bd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-05T11:01:03Z</t>
-  </si>
-  <si>
-    <t>ae1827f51a8ec3373f0efd8320c0db4d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.7fb50e92af^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-05T11:05:33Z</t>
-  </si>
-  <si>
-    <t>162e5f0ff40a0864717ab5a919508297</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.e86bec11f0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-10T10:38:46Z</t>
+  </si>
+  <si>
+    <t>696835a3cfecb4a212b17a3ee0ff042e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.8271936742^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-10T10:16:27Z</t>
+  </si>
+  <si>
+    <t>2e9a66e939926d6506517170a0912e3c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.1098f93fe8^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-10T10:46:13Z</t>
+  </si>
+  <si>
+    <t>115cfa19dd816342794e332559428b00</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.bb760ec4e3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -11151,16 +11151,16 @@
         <v>433</v>
       </c>
       <c r="F191" s="51">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="G191" s="52" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="H191" s="52" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="I191" s="52" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="J191" s="38" t="s">
         <v>64</v>
@@ -11198,16 +11198,16 @@
         <v>434</v>
       </c>
       <c r="F192" s="53">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="G192" s="52" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H192" s="52" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I192" s="52" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J192" s="38" t="s">
         <v>64</v>
@@ -11245,16 +11245,16 @@
         <v>437</v>
       </c>
       <c r="F193" s="37">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="G193" s="37" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H193" s="37" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I193" s="42" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J193" s="38" t="s">
         <v>64</v>
@@ -17508,6 +17508,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17651,22 +17666,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17684,31 +17709,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/A1#111#TS23XX/TS23/TServe/V.1.4.46.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#TS23XX/TS23/TServe/V.1.4.46.0/accreditamento-checklist_V8.2.7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\Desktop\TServe\Accreditamento bis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B393B7-DE76-4C50-BD07-1AF360E44321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7B6E5A-BE8C-4228-AB5A-91335AE14C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4515" yWindow="2625" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1783,24 +1783,6 @@
     <t>subject_application_id: TServe</t>
   </si>
   <si>
-    <t>2026-03-10T10:38:46Z</t>
-  </si>
-  <si>
-    <t>696835a3cfecb4a212b17a3ee0ff042e</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.8271936742^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-10T10:16:27Z</t>
-  </si>
-  <si>
-    <t>2e9a66e939926d6506517170a0912e3c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.1098f93fe8^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-10T10:46:13Z</t>
   </si>
   <si>
@@ -1808,6 +1790,24 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.bb760ec4e3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-12T08:40:07Z</t>
+  </si>
+  <si>
+    <t>9ae7e2b7bc601e88f036da2c41e31416</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.1bc6db366e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-12T08:48:27Z</t>
+  </si>
+  <si>
+    <t>10b17d7d95cf0d9f7683ae8ac5b3644e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.c9c78af83f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -11154,13 +11154,13 @@
         <v>46091</v>
       </c>
       <c r="G191" s="52" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="H191" s="52" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="I191" s="52" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="J191" s="38" t="s">
         <v>64</v>
@@ -11198,16 +11198,16 @@
         <v>434</v>
       </c>
       <c r="F192" s="53">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="G192" s="52" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="H192" s="52" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I192" s="52" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J192" s="38" t="s">
         <v>64</v>
@@ -11245,16 +11245,16 @@
         <v>437</v>
       </c>
       <c r="F193" s="37">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="G193" s="37" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H193" s="37" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I193" s="42" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J193" s="38" t="s">
         <v>64</v>
@@ -17508,21 +17508,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17666,32 +17651,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17709,6 +17684,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
